--- a/final data.xlsx
+++ b/final data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Desktop\Remittance-Inflow-Analysis-and-Forecasting\.git\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Desktop\Remittance-Inflow-Analysis-and-Forecasting\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0B66D1CB-582D-4080-A703-4F495C1DE82C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42EE1AD0-738F-4AB4-AFCE-4FB09F728C72}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BD832F46-A82B-CD40-8203-AECA3879CEB5}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>Year</t>
   </si>
@@ -43,6 +43,9 @@
   </si>
   <si>
     <t>Exchange rate(US$ to NPR)</t>
+  </si>
+  <si>
+    <t>abc</t>
   </si>
 </sst>
 </file>
@@ -430,7 +433,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E27EA996-B1A6-6742-9499-CE592365FF59}">
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="11.08984375" bestFit="1" customWidth="1"/>
@@ -439,7 +442,7 @@
     <col min="6" max="6" width="21.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -459,7 +462,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:8">
       <c r="A2" s="1">
         <v>1993</v>
       </c>
@@ -479,7 +482,7 @@
         <v>62.75</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:8">
       <c r="A3" s="1">
         <v>1994</v>
       </c>
@@ -499,7 +502,7 @@
         <v>62.75</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:8">
       <c r="A4" s="1">
         <v>1995</v>
       </c>
@@ -519,7 +522,7 @@
         <v>62.75</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:8">
       <c r="A5" s="1">
         <v>1996</v>
       </c>
@@ -539,7 +542,7 @@
         <v>62.75</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:8">
       <c r="A6" s="1">
         <v>1997</v>
       </c>
@@ -558,8 +561,11 @@
       <c r="F6">
         <v>62.75</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
+      <c r="H6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="1">
         <v>1998</v>
       </c>
@@ -579,7 +585,7 @@
         <v>66.319999999999993</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:8">
       <c r="A8" s="1">
         <v>1999</v>
       </c>
@@ -599,7 +605,7 @@
         <v>68.05</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:8">
       <c r="A9" s="1">
         <v>2000</v>
       </c>
@@ -619,7 +625,7 @@
         <v>71.489999999999995</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:8">
       <c r="A10" s="1">
         <v>2001</v>
       </c>
@@ -639,7 +645,7 @@
         <v>75.47</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:8">
       <c r="A11" s="1">
         <v>2002</v>
       </c>
@@ -659,7 +665,7 @@
         <v>78.290000000000006</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:8">
       <c r="A12" s="1">
         <v>2003</v>
       </c>
@@ -679,7 +685,7 @@
         <v>76.260000000000005</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:8">
       <c r="A13" s="1">
         <v>2004</v>
       </c>
@@ -699,7 +705,7 @@
         <v>73.930000000000007</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:8">
       <c r="A14" s="1">
         <v>2005</v>
       </c>
@@ -719,7 +725,7 @@
         <v>71.72</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:8">
       <c r="A15" s="1">
         <v>2006</v>
       </c>
@@ -739,7 +745,7 @@
         <v>73.12</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:8">
       <c r="A16" s="1">
         <v>2007</v>
       </c>

--- a/final data.xlsx
+++ b/final data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Desktop\Remittance-Inflow-Analysis-and-Forecasting\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42EE1AD0-738F-4AB4-AFCE-4FB09F728C72}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFBB6112-8668-4387-8A61-2ACF05364671}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BD832F46-A82B-CD40-8203-AECA3879CEB5}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>Year</t>
   </si>
@@ -43,9 +43,6 @@
   </si>
   <si>
     <t>Exchange rate(US$ to NPR)</t>
-  </si>
-  <si>
-    <t>abc</t>
   </si>
 </sst>
 </file>
@@ -433,7 +430,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E27EA996-B1A6-6742-9499-CE592365FF59}">
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="11.08984375" bestFit="1" customWidth="1"/>
@@ -442,7 +439,7 @@
     <col min="6" max="6" width="21.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -462,7 +459,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:6">
       <c r="A2" s="1">
         <v>1993</v>
       </c>
@@ -482,7 +479,7 @@
         <v>62.75</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:6">
       <c r="A3" s="1">
         <v>1994</v>
       </c>
@@ -502,7 +499,7 @@
         <v>62.75</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:6">
       <c r="A4" s="1">
         <v>1995</v>
       </c>
@@ -522,7 +519,7 @@
         <v>62.75</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:6">
       <c r="A5" s="1">
         <v>1996</v>
       </c>
@@ -542,7 +539,7 @@
         <v>62.75</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:6">
       <c r="A6" s="1">
         <v>1997</v>
       </c>
@@ -561,11 +558,8 @@
       <c r="F6">
         <v>62.75</v>
       </c>
-      <c r="H6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" s="1">
         <v>1998</v>
       </c>
@@ -585,7 +579,7 @@
         <v>66.319999999999993</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:6">
       <c r="A8" s="1">
         <v>1999</v>
       </c>
@@ -605,7 +599,7 @@
         <v>68.05</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:6">
       <c r="A9" s="1">
         <v>2000</v>
       </c>
@@ -625,7 +619,7 @@
         <v>71.489999999999995</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:6">
       <c r="A10" s="1">
         <v>2001</v>
       </c>
@@ -645,7 +639,7 @@
         <v>75.47</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:6">
       <c r="A11" s="1">
         <v>2002</v>
       </c>
@@ -665,7 +659,7 @@
         <v>78.290000000000006</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:6">
       <c r="A12" s="1">
         <v>2003</v>
       </c>
@@ -685,7 +679,7 @@
         <v>76.260000000000005</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:6">
       <c r="A13" s="1">
         <v>2004</v>
       </c>
@@ -705,7 +699,7 @@
         <v>73.930000000000007</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:6">
       <c r="A14" s="1">
         <v>2005</v>
       </c>
@@ -725,7 +719,7 @@
         <v>71.72</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:6">
       <c r="A15" s="1">
         <v>2006</v>
       </c>
@@ -745,7 +739,7 @@
         <v>73.12</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:6">
       <c r="A16" s="1">
         <v>2007</v>
       </c>
